--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,511 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129733174</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75187</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Porsbackarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544256</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6780662</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alfta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129733177</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98685</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Porsbackarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>544307</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6780663</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alfta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129733173</v>
+      </c>
+      <c r="B6" t="n">
+        <v>82910</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Porsbackarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544260</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6780678</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alfta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129733175</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Porsbackarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544280</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6780662</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alfta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129733181</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98685</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Porsbackarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>544316</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6780631</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alfta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129733174</v>
       </c>
       <c r="B4" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129733174</v>
       </c>
       <c r="B4" t="n">
-        <v>75188</v>
+        <v>75193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98686</v>
+        <v>98691</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98691</v>
+        <v>98695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98691</v>
+        <v>98695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98695</v>
+        <v>98697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98697</v>
+        <v>98707</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129733174</v>
       </c>
       <c r="B4" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98707</v>
+        <v>98711</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129733174</v>
       </c>
       <c r="B4" t="n">
-        <v>75196</v>
+        <v>75199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98711</v>
+        <v>98714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98714</v>
+        <v>98715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 19180-2024 artfynd.xlsx
+++ b/artfynd/A 19180-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129733174</v>
       </c>
       <c r="B4" t="n">
-        <v>75199</v>
+        <v>75200</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129733177</v>
       </c>
       <c r="B5" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>129733173</v>
       </c>
       <c r="B6" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>129733175</v>
       </c>
       <c r="B7" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>129733181</v>
       </c>
       <c r="B8" t="n">
-        <v>98715</v>
+        <v>98732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
